--- a/PopEyez requirements.xlsx
+++ b/PopEyez requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Desktop\GUC\SEMESTER 6\Software Engineering\Project\PopEyez\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonyj\OneDrive\Desktop\projects\PopEyez\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B496BD-1B14-4B66-BD06-F29FF0187089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A0B25-CFAB-44AE-B65B-BA50535A5F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Info" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="213">
   <si>
     <t>Team Name</t>
   </si>
@@ -565,6 +565,111 @@
   </si>
   <si>
     <t>youssef.shenoda@student.giu-berlin.de</t>
+  </si>
+  <si>
+    <t>Event Planning Module - Budget Management</t>
+  </si>
+  <si>
+    <t>FR-EPB-01</t>
+  </si>
+  <si>
+    <t>manage budget categories and spending limits</t>
+  </si>
+  <si>
+    <t>I can plan the event's money.</t>
+  </si>
+  <si>
+    <t>FR-EPB-02</t>
+  </si>
+  <si>
+    <t>manage and track specific costs under my budget categories</t>
+  </si>
+  <si>
+    <t>I can keep track of what I actually spend.</t>
+  </si>
+  <si>
+    <t>FR-EPB-03</t>
+  </si>
+  <si>
+    <t>create and download budget reports</t>
+  </si>
+  <si>
+    <t>I can review the final costs of the event.</t>
+  </si>
+  <si>
+    <t>Vendor Management Module - Sourcing Requests</t>
+  </si>
+  <si>
+    <t>FR-VMS-01</t>
+  </si>
+  <si>
+    <t>send and cancel requests to vendors</t>
+  </si>
+  <si>
+    <t>I can know their prices and see if they can supply what I need.</t>
+  </si>
+  <si>
+    <t>FR-VMS-02</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>read requests sent by the organizer and reply with my prices and details</t>
+  </si>
+  <si>
+    <t>the organizer can decide whether to buy from me.</t>
+  </si>
+  <si>
+    <t>FR-VMS-03</t>
+  </si>
+  <si>
+    <t>check and accept or decline a vendor's price offer</t>
+  </si>
+  <si>
+    <t>I can choose who to buy from.</t>
+  </si>
+  <si>
+    <t>FR-VMS-04</t>
+  </si>
+  <si>
+    <t>change the delivery status of an order</t>
+  </si>
+  <si>
+    <t>the organizer can track the delivery of the supplies.</t>
+  </si>
+  <si>
+    <t>FR-VMS-05</t>
+  </si>
+  <si>
+    <t>mark I received the delivery</t>
+  </si>
+  <si>
+    <t>the system knows the order is complete.</t>
+  </si>
+  <si>
+    <t>Vendor Management Module - Invoice Management</t>
+  </si>
+  <si>
+    <t>FR-VMI-01</t>
+  </si>
+  <si>
+    <t>manage and issue invoices for finished orders</t>
+  </si>
+  <si>
+    <t>I can get paid.</t>
+  </si>
+  <si>
+    <t>FR-VMI-01,FR-EPB-01</t>
+  </si>
+  <si>
+    <t>FR-VMI-02</t>
+  </si>
+  <si>
+    <t>review and accept vendor invoices</t>
+  </si>
+  <si>
+    <t>I can approve payment and update my budget.</t>
   </si>
 </sst>
 </file>
@@ -1038,6 +1143,10 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1053,10 +1162,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1261,38 +1366,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
     </row>
     <row r="2" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="66"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
@@ -1357,7 +1462,7 @@
       <c r="B10" s="10">
         <v>22001212</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="66" t="s">
         <v>177</v>
       </c>
       <c r="D10" s="10">
@@ -1404,29 +1509,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="68" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="70" t="s">
         <v>14</v>
       </c>
       <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
       <c r="D2" s="15" t="s">
         <v>15</v>
       </c>
@@ -1436,7 +1541,7 @@
       <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="68"/>
+      <c r="G2" s="70"/>
       <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
@@ -2173,8 +2278,8 @@
       </c>
       <c r="G32" s="62"/>
     </row>
-    <row r="33" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="70" t="s">
+    <row r="33" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A33" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B33" s="18"/>
@@ -2192,8 +2297,8 @@
       </c>
       <c r="G33" s="20"/>
     </row>
-    <row r="34" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
+    <row r="34" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A34" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B34" s="18" t="s">
@@ -2213,8 +2318,8 @@
       </c>
       <c r="G34" s="20"/>
     </row>
-    <row r="35" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="70" t="s">
+    <row r="35" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A35" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B35" s="18" t="s">
@@ -2234,8 +2339,8 @@
       </c>
       <c r="G35" s="20"/>
     </row>
-    <row r="36" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="70" t="s">
+    <row r="36" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A36" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B36" s="18" t="s">
@@ -2255,8 +2360,8 @@
       </c>
       <c r="G36" s="20"/>
     </row>
-    <row r="37" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="70" t="s">
+    <row r="37" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A37" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B37" s="18" t="s">
@@ -2276,8 +2381,8 @@
       </c>
       <c r="G37" s="20"/>
     </row>
-    <row r="38" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="70" t="s">
+    <row r="38" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A38" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B38" s="18" t="s">
@@ -2297,8 +2402,8 @@
       </c>
       <c r="G38" s="20"/>
     </row>
-    <row r="39" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="70" t="s">
+    <row r="39" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A39" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B39" s="18" t="s">
@@ -2318,8 +2423,8 @@
       </c>
       <c r="G39" s="20"/>
     </row>
-    <row r="40" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="70" t="s">
+    <row r="40" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A40" s="65" t="s">
         <v>141</v>
       </c>
       <c r="B40" s="18" t="s">
@@ -2339,8 +2444,8 @@
       </c>
       <c r="G40" s="20"/>
     </row>
-    <row r="41" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="70" t="s">
+    <row r="41" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A41" s="65" t="s">
         <v>169</v>
       </c>
       <c r="B41" s="18" t="s">
@@ -2360,8 +2465,8 @@
       </c>
       <c r="G41" s="20"/>
     </row>
-    <row r="42" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="70" t="s">
+    <row r="42" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A42" s="65" t="s">
         <v>169</v>
       </c>
       <c r="B42" s="18" t="s">
@@ -2382,93 +2487,209 @@
       <c r="G42" s="20"/>
     </row>
     <row r="43" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
+      <c r="A43" s="17" t="s">
+        <v>178</v>
+      </c>
       <c r="B43" s="18"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="21"/>
+      <c r="C43" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>181</v>
+      </c>
       <c r="G43" s="20"/>
     </row>
     <row r="44" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="21"/>
+      <c r="A44" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>184</v>
+      </c>
       <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="21"/>
+      <c r="A45" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>187</v>
+      </c>
       <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
+      <c r="A46" s="17" t="s">
+        <v>188</v>
+      </c>
       <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="21"/>
+      <c r="C46" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>191</v>
+      </c>
       <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="21"/>
+      <c r="A47" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>195</v>
+      </c>
       <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="21"/>
+      <c r="A48" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>198</v>
+      </c>
       <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="34"/>
-      <c r="B49" s="35"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="38"/>
+      <c r="A49" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>201</v>
+      </c>
       <c r="G49" s="20"/>
     </row>
     <row r="50" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="25"/>
+      <c r="A50" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>204</v>
+      </c>
       <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="39"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
+      <c r="A51" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="B51" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="C51" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D51" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>208</v>
+      </c>
       <c r="G51" s="22"/>
     </row>
     <row r="52" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="39"/>
-      <c r="B52" s="39"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
+      <c r="A52" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>212</v>
+      </c>
       <c r="G52" s="22"/>
     </row>
     <row r="53" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">

--- a/PopEyez requirements.xlsx
+++ b/PopEyez requirements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonyj\OneDrive\Desktop\projects\PopEyez\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d82daf92372a5c5a/Desktop/projects/PopEyez/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A0B25-CFAB-44AE-B65B-BA50535A5F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E69A0B25-CFAB-44AE-B65B-BA50535A5F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2669907C-96B3-48BF-BE23-345705B145F3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="9970" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Info" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="215">
   <si>
     <t>Team Name</t>
   </si>
@@ -670,6 +670,12 @@
   </si>
   <si>
     <t>I can approve payment and update my budget.</t>
+  </si>
+  <si>
+    <t>Tony John Safwat Gendy</t>
+  </si>
+  <si>
+    <t>tony.gendy@student.giu-berlin.de</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1003,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1147,6 +1153,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1156,12 +1168,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1366,38 +1373,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
     </row>
     <row r="2" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
@@ -1470,10 +1477,18 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="A11" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" s="12">
+        <v>22001215</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="12">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
@@ -1489,6 +1504,7 @@
     <hyperlink ref="C8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C9" r:id="rId3" xr:uid="{693CED25-6D74-40F0-ABD4-E90771578C28}"/>
     <hyperlink ref="C10" r:id="rId4" xr:uid="{55D1C066-3F5F-4DDC-ABBD-5BC351D74261}"/>
+    <hyperlink ref="C11" r:id="rId5" xr:uid="{3FF22B8B-602F-4D46-823E-CD5FCEB28965}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1509,29 +1525,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="C1" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="70" t="s">
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="67" t="s">
         <v>14</v>
       </c>
       <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
       <c r="D2" s="15" t="s">
         <v>15</v>
       </c>
@@ -1541,7 +1557,7 @@
       <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="70"/>
+      <c r="G2" s="67"/>
       <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
